--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575201114</v>
+        <v>46157.93119364326</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93119364326</v>
+        <v>46157.93185122984</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93185122984</v>
+        <v>46157.93406593064</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406593064</v>
+        <v>46157.93724649811</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93724649811</v>
+        <v>46158.28222323978</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222323978</v>
+        <v>46158.29708270273</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29708270273</v>
+        <v>46158.29822235261</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29822235261</v>
+        <v>46158.33393274539</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33393274539</v>
+        <v>46158.36863066367</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36863066367</v>
+        <v>46158.37294024965</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
